--- a/docs/business/ForgeFlow Project Cost.xlsx
+++ b/docs/business/ForgeFlow Project Cost.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Category Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cost Details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="D13" s="87" t="inlineStr">
         <is>
-          <t>Firebase Cloud Functions / Google Cloud / Security Rules</t>
+          <t>Supabase / PostgreSQL / Row-Level Security / Google Cloud Run / Cloud Functions</t>
         </is>
       </c>
       <c r="E13" s="74" t="n"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D14" s="83" t="inlineStr">
         <is>
-          <t>Firebase Auth / Firestore / Firebase Admin SDK</t>
+          <t>Firebase Auth / Supabase PostgreSQL / Postgres Row-Level Security</t>
         </is>
       </c>
       <c r="E14" s="74" t="n"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B44" s="82" t="inlineStr">
         <is>
-          <t>Cloud hosting (Firebase)</t>
+          <t>Cloud hosting (Firebase Auth + Supabase + Cloud Run)</t>
         </is>
       </c>
       <c r="C44" s="55" t="n">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D44" s="89" t="inlineStr">
         <is>
-          <t>Firebase (Auth, Firestore, Functions, Storage)</t>
+          <t>Firebase Auth + Supabase (PostgreSQL, Realtime, Storage) + Google Cloud Run</t>
         </is>
       </c>
       <c r="E44" s="74" t="n"/>
